--- a/в бланки заводов/Останкино КИ/ostankino_ki/UZ/чистый бланк/Бланк заказа Mos prod Torg 11.12.25.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/UZ/чистый бланк/Бланк заказа Mos prod Torg 11.12.25.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52039A44-C7B1-47D7-86FE-8F6C5634C0E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D039455-E805-4506-A480-6A5ABBD6B47E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">машины!$A$9:$I$104</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1691,7 +1691,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="43">
-        <v>46017</v>
+        <v>46034</v>
       </c>
       <c r="E3" s="51" t="s">
         <v>1</v>
@@ -2894,14 +2894,14 @@
         <v>41</v>
       </c>
       <c r="C56" s="62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D56" s="70">
         <v>1001035277059</v>
       </c>
       <c r="E56" s="56"/>
       <c r="F56" s="14">
-        <f>E56</f>
+        <f>E56*0.3</f>
         <v>0</v>
       </c>
       <c r="G56" s="14"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/UZ/чистый бланк/Бланк заказа Mos prod Torg 11.12.25.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/UZ/чистый бланк/Бланк заказа Mos prod Torg 11.12.25.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D039455-E805-4506-A480-6A5ABBD6B47E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92429905-6390-456A-871A-C04F6EC27FBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,9 +358,6 @@
     <t>МОЛОЧНЫЕ КЛАССИЧЕСКИЕ сос п/о в/у 0.3кг</t>
   </si>
   <si>
-    <t>СОЧНЫЕ ПМ сос п/о мгс 1*6_СНГ</t>
-  </si>
-  <si>
     <t>МЯСНЫЕ Папа может сар б/о мгс 1*3_Х5_45с</t>
   </si>
   <si>
@@ -371,6 +368,9 @@
   </si>
   <si>
     <t>СЕРВЕЛАТ КАРЕЛЬС.вк в/у 0.28кг_СНГ_209к</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ ПМ сос п/о мгс 1.5*4_А_50с</t>
   </si>
 </sst>
 </file>
@@ -1691,7 +1691,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="43">
-        <v>46034</v>
+        <v>46042</v>
       </c>
       <c r="E3" s="51" t="s">
         <v>1</v>
@@ -1827,7 +1827,7 @@
         <v>7231</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>19</v>
@@ -2717,7 +2717,7 @@
         <v>7070</v>
       </c>
       <c r="B48" s="67" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C48" s="62" t="s">
         <v>18</v>
@@ -2845,7 +2845,7 @@
         <v>6549</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C54" s="62" t="s">
         <v>18</v>
@@ -2937,7 +2937,7 @@
         <v>6548</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C58" s="62" t="s">
         <v>18</v>
@@ -3147,7 +3147,7 @@
         <v>7230</v>
       </c>
       <c r="B68" s="67" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C68" s="62" t="s">
         <v>19</v>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/UZ/чистый бланк/Бланк заказа Mos prod Torg 11.12.25.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/UZ/чистый бланк/Бланк заказа Mos prod Torg 11.12.25.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92429905-6390-456A-871A-C04F6EC27FBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06D7D9A-10F7-4326-B900-F74597A15EE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1691,7 +1691,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="43">
-        <v>46042</v>
+        <v>46049</v>
       </c>
       <c r="E3" s="51" t="s">
         <v>1</v>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/UZ/чистый бланк/Бланк заказа Mos prod Torg 11.12.25.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/UZ/чистый бланк/Бланк заказа Mos prod Torg 11.12.25.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06D7D9A-10F7-4326-B900-F74597A15EE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B793ED5F-19D4-4317-98F9-70C6604138B7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1691,7 +1691,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="43">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="E3" s="51" t="s">
         <v>1</v>
